--- a/results/5judge_decisions.xlsx
+++ b/results/5judge_decisions.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>102</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
